--- a/faq/deposits.xlsx
+++ b/faq/deposits.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,486 +450,76 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Все вклады в банке застрахованы.'</t>
+          <t xml:space="preserve">  - 'Уралсиб состоит в реестре банков - участников системы обязательного страхования вкладов.'</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Все вклады в банке застрахованы.</t>
+          <t xml:space="preserve">  - 'Уралсиб состоит в реестре банков-участников системы обязательного страхования вкладов.'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>«банков - участников» — дефис в сложном слове написан отдельно, как тире; исправлено на слитное дефисное написание</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Уралсиб состоит в реестре банков - участников системы обязательного страхования вкладов.'</t>
+          <t xml:space="preserve">      • Проценты рассчитываются в день страхового случая</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Уралсиб состоит в реестре банков-участников системы обязательного страхования вкладов.</t>
+          <t xml:space="preserve">      • Проценты рассчитываются в день страхового случая.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>«банков - участников» — дефис в сложном слове написан с пробелами как тире; исправлено на слитное дефисное написание «банков-участников»</t>
+          <t>добавлена точка в конце пункта — для единообразия со вторым пунктом списка (стр. 8), где точка есть</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    При наступлении страхового случая:</t>
+          <t xml:space="preserve">  - 'Налог оплачивается с процентов по вкладам и остатках на счетах, если они превышают определенный лимит.'</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>При наступлении страхового случая:</t>
+          <t xml:space="preserve">  - 'Налог оплачивается с процентов по вкладам и остатков на счетах, если они превышают определенный лимит.'</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>«остатках» исправлено на «остатков» — согласование падежа: «с процентов ... и остатков» (родительный падеж после «с»)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      • Проценты рассчитываются в день страхового случая</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>• Проценты рассчитываются в день страхового случая.</t>
+          <t xml:space="preserve">  - 'Расчет лимита: 1 млн рублей и умножается на максимальную ключевую ставку ЦБ РФ за налоговый период. В 2024 году ключевая ставка — 21%. Лимит равен 210 000 рублей.'</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>добавлена точка — для единообразия со вторым пунктом списка (стр. 8), у которого точка есть</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • По валютным счетам проценты выплачиваются в рублях по курсу ЦБ РФ на дату страхового случая.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>• По валютным счетам проценты выплачиваются в рублях по курсу ЦБ РФ на дату страхового случая.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Если в банке несколько вкладов, возмещение выплачивается пропорционально размеру каждого вклада, но не более максимального размера возмещения.'</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Если в банке несколько вкладов, возмещение выплачивается пропорционально размеру каждого вклада, но не более максимального размера возмещения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  'Проценты по вкладу застрахованы, если по условиям договора они начисляются на счет вклада.'</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Проценты по вкладу застрахованы, если по условиям договора они начисляются на счет вклада.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Налог оплачивается с процентов по вкладам и остатках на счетах, если они превышают определенный лимит.'</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Налог оплачивается с процентов по вкладам и остатков на счетах, если они превышают определенный лимит.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>«остатках» исправлено на «остатков» — согласование падежа: «с процентов ... и остатков» (родительный падеж после «с»)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Расчет лимита: 1 млн рублей и умножается на максимальную ключевую ставку ЦБ РФ за налоговый период. В 2024 году ключевая ставка — 21%. Лимит равен 210 000 рублей.'</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Расчет лимита: 1 млн рублей и умножается на максимальную ключевую ставку ЦБ РФ за налоговый период. В 2024 году ключевая ставка — 21%. Лимит равен 210 000 рублей.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>сомнительное место: «1 млн рублей и умножается на максимальную ключевую ставку» — грамматически не согласовано (лишнее «и» или пропущено подлежащее). Похоже, должно быть «1 млн рублей умножается на максимальную ключевую ставку». Не стал менять сам, так как это не просто орфография/пунктуация, а возможная пропажа/лишнее слово — нужна проверка по смыслу</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>17</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Для открытия счета гражданину РФ нужно предоставить один из документов:</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Для открытия счета гражданину РФ нужно предоставить один из документов:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>18</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Паспорт</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>• Паспорт</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Загранпаспорт, дипломатический паспорт, служебный паспорт</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>• Загранпаспорт, дипломатический паспорт, служебный паспорт</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>20</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Временное удостоверение личности, выданное на период оформления паспорта</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>• Временное удостоверение личности, выданное на период оформления паспорта</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>22</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Другие документы, удостоверяющие личность:</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Другие документы, удостоверяющие личность:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>23</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Для граждан РФ младше 14 лет — свидетельство о рождении</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>• Для граждан РФ младше 14 лет — свидетельство о рождении</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • При наличии приложить ИНН и СНИЛС</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>• При наличии приложить ИНН и СНИЛС</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>27</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Для несовершеннолетних граждан РФ:</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Для несовершеннолетних граждан РФ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>28</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • От 14 лет: паспорт, согласие и паспорт законного представителя</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>• От 14 лет: паспорт, согласие и паспорт законного представителя</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • До 14 лет: свидетельство о рождении и паспорт законного представителя</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>• До 14 лет: свидетельство о рождении и паспорт законного представителя</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>31</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Для несовершеннолетних иностранных граждан: паспорт или другой документ, удостоверяющий личность</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Для несовершеннолетних иностранных граждан: паспорт или другой документ, удостоверяющий личность</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>34</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Для открытия счета иностранному гражданину нужно предоставить один из документов:</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Для открытия счета иностранному гражданину нужно предоставить один из документов:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Паспорт иностранного гражданина</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>• Паспорт иностранного гражданина</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Другой документ, удостоверяющий личность</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>• Другой документ, удостоверяющий личность</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>38</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Лицам без гражданства, постоянно проживающим на территории РФ:</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Лицам без гражданства, постоянно проживающим на территории РФ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>39</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Вид на жительство</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>• Вид на жительство</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>40</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Лицам без гражданства, не проживающим постоянно на территории РФ:</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Лицам без гражданства, не проживающим постоянно на территории РФ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>41</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Документ, удостоверяющий личность, выданный другим государством</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>• Документ, удостоверяющий личность, выданный другим государством</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>42</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Вид на жительство</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>• Вид на жительство</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>43</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Разрешение на временное проживание</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>• Разрешение на временное проживание</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>46</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Удостоверение беженца</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>• Удостоверение беженца</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>47</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Свидетельство о рассмотрении ходатайства о признании лица беженцем</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>• Свидетельство о рассмотрении ходатайства о признании лица беженцем</t>
+          <t>сомнительное место: «1 млн рублей и умножается на максимальную ключевую ставку» — грамматически не согласовано. Похоже, должно быть «1 млн рублей умножается на максимальную ключевую ставку» (лишнее «и»). Не исправлял сам — требуется проверка по смыслу</t>
         </is>
       </c>
     </row>
